--- a/DataProvider/DataSheets.xlsx
+++ b/DataProvider/DataSheets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8340"/>
   </bookViews>
   <sheets>
     <sheet name="Merchandiser" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Year</t>
   </si>
@@ -60,19 +60,16 @@
     <t>Reliance</t>
   </si>
   <si>
-    <t>Reliance Merchandising</t>
-  </si>
-  <si>
-    <t>Dusty</t>
-  </si>
-  <si>
-    <t>Purdy</t>
-  </si>
-  <si>
-    <t>dusty.purdy26@gmail.com</t>
-  </si>
-  <si>
-    <t>Inspection of Stock</t>
+    <t>Physical re-stock</t>
+  </si>
+  <si>
+    <t>Cameron</t>
+  </si>
+  <si>
+    <t>Nikolaus</t>
+  </si>
+  <si>
+    <t>cameron.nikolas94@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -418,12 +415,14 @@
   <cols>
     <col min="1" max="1" width="36.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -475,10 +474,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="2">
-        <v>753951</v>
+        <v>953548</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>14</v>
@@ -490,16 +489,16 @@
         <v>456789123</v>
       </c>
       <c r="I2" s="5">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
